--- a/public/exports/11259979.xlsx
+++ b/public/exports/11259979.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports/11259979.xlsx
+++ b/public/exports/11259979.xlsx
@@ -1466,17 +1466,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beringsvej 8</t>
+          <t xml:space="preserve">Frederiksberg Alle 48</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1820</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030255</t>
+          <t xml:space="preserve">100025821</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="J20">
-        <v>413</v>
+        <v>996</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218022</t>
+          <t xml:space="preserve">311217955</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Alle 48</t>
+          <t xml:space="preserve">Segelckesvej 7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025821</t>
+          <t xml:space="preserve">100030239</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="J21">
-        <v>996</v>
+        <v>408</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217955</t>
+          <t xml:space="preserve">311223800</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-15</t>
+          <t xml:space="preserve">2027-01-21</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1616,17 +1616,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segelckesvej 7</t>
+          <t xml:space="preserve">Thorvaldsensvej 24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030239</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1635,11 +1635,11 @@
         </is>
       </c>
       <c r="J22">
-        <v>408</v>
+        <v>3792</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223800</t>
+          <t xml:space="preserve">311223802</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 24</t>
+          <t xml:space="preserve">Storm Petersens Vej 5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100047575</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1710,21 +1710,21 @@
         </is>
       </c>
       <c r="J23">
-        <v>3792</v>
+        <v>297</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223802</t>
+          <t xml:space="preserve">311225730</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-21</t>
+          <t xml:space="preserve">2027-01-31</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 5</t>
+          <t xml:space="preserve">Hortensiavej 11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047575</t>
+          <t xml:space="preserve">100025624</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1785,11 +1785,11 @@
         </is>
       </c>
       <c r="J24">
-        <v>297</v>
+        <v>440</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225730</t>
+          <t xml:space="preserve">311226748</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-31</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 11</t>
+          <t xml:space="preserve">Hortensiavej 13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025624</t>
+          <t xml:space="preserve">100025599</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="J25">
-        <v>440</v>
+        <v>255</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226748</t>
+          <t xml:space="preserve">311226749</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">230</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 13</t>
+          <t xml:space="preserve">Biskop Svanes Vej 75</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">3460</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025599</t>
+          <t xml:space="preserve">8312706</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="J26">
-        <v>255</v>
+        <v>1322</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226749</t>
+          <t xml:space="preserve">311231330</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1986,22 +1986,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">230</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biskop Svanes Vej 75</t>
+          <t xml:space="preserve">Nørrevænget 14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3460</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8312706</t>
+          <t xml:space="preserve">2137707</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,11 +2010,11 @@
         </is>
       </c>
       <c r="J27">
-        <v>1322</v>
+        <v>295</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231330</t>
+          <t xml:space="preserve">311227340</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 14</t>
+          <t xml:space="preserve">Amicisvej 9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137707</t>
+          <t xml:space="preserve">100025655</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="J28">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227340</t>
+          <t xml:space="preserve">311227832</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 9</t>
+          <t xml:space="preserve">Bülowsvej 14A</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025655</t>
+          <t xml:space="preserve">100026669</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,11 +2160,11 @@
         </is>
       </c>
       <c r="J29">
-        <v>340</v>
+        <v>626</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227832</t>
+          <t xml:space="preserve">311227831</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 14A</t>
+          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026669</t>
+          <t xml:space="preserve">100025685</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="J30">
-        <v>626</v>
+        <v>953</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227831</t>
+          <t xml:space="preserve">311229051</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
+          <t xml:space="preserve">Frydendalsvej 19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025685</t>
+          <t xml:space="preserve">100028929</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>953</v>
+        <v>805</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229051</t>
+          <t xml:space="preserve">311229048</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 19</t>
+          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">1904</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028929</t>
+          <t xml:space="preserve">100027090</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2385,21 +2385,21 @@
         </is>
       </c>
       <c r="J32">
-        <v>805</v>
+        <v>589</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229048</t>
+          <t xml:space="preserve">311230550</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-17</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
+          <t xml:space="preserve">Junggreensvej 12B</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027090</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>589</v>
+        <v>1152</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230550</t>
+          <t xml:space="preserve">311230598</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2516,30 +2516,30 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junggreensvej 12B</t>
+          <t xml:space="preserve">N.J. Fjords Alle 15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100026522</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J34">
-        <v>1152</v>
+        <v>300</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230598</t>
+          <t xml:space="preserve">311230618</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 15</t>
+          <t xml:space="preserve">N.J. Fjords Alle 17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2606,11 +2606,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J35">
-        <v>300</v>
+        <v>376</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,30 +2666,30 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 17</t>
+          <t xml:space="preserve">Nyelandsvej 66</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026522</t>
+          <t xml:space="preserve">100029714</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230618</t>
+          <t xml:space="preserve">311230609</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 75</t>
+          <t xml:space="preserve">Sankt Knuds Vej 7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029720</t>
+          <t xml:space="preserve">100026917</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,11 +2760,11 @@
         </is>
       </c>
       <c r="J37">
-        <v>1334</v>
+        <v>433</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230619</t>
+          <t xml:space="preserve">311230540</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 66</t>
+          <t xml:space="preserve">Bakkegårds Alle 18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1804</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029714</t>
+          <t xml:space="preserve">191034</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="J38">
-        <v>342</v>
+        <v>1225</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230609</t>
+          <t xml:space="preserve">311230651</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 7</t>
+          <t xml:space="preserve">Dronning Olgas Vej 6</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026917</t>
+          <t xml:space="preserve">100028120</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>433</v>
+        <v>580</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230540</t>
+          <t xml:space="preserve">311230652</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkegårds Alle 18</t>
+          <t xml:space="preserve">Rahbeks Alle 19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804</t>
+          <t xml:space="preserve">1801</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">191034</t>
+          <t xml:space="preserve">100028743</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J40">
-        <v>1225</v>
+        <v>388</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230651</t>
+          <t xml:space="preserve">311231234</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3036,22 +3036,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Olgas Vej 6</t>
+          <t xml:space="preserve">Skærbygårdsvej 15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028120</t>
+          <t xml:space="preserve">5347084</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>580</v>
+        <v>1209</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230652</t>
+          <t xml:space="preserve">311231683</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 40</t>
+          <t xml:space="preserve">Thorvaldsensvej 26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029487</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J42">
-        <v>1071</v>
+        <v>422</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231229</t>
+          <t xml:space="preserve">311233222</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahbeks Alle 19</t>
+          <t xml:space="preserve">Oddenvej 90B</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028743</t>
+          <t xml:space="preserve">2428914</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231234</t>
+          <t xml:space="preserve">311233782</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3261,35 +3261,35 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skærbygårdsvej 15</t>
+          <t xml:space="preserve">Skellet 27A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5347084</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J44">
-        <v>1209</v>
+        <v>476</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231683</t>
+          <t xml:space="preserve">311233769</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-02</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 26</t>
+          <t xml:space="preserve">Vodroffsvej 46</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">1900</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100027252</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J45">
-        <v>422</v>
+        <v>1486</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233222</t>
+          <t xml:space="preserve">311234441</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oddenvej 90B</t>
+          <t xml:space="preserve">Allegade 31</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428914</t>
+          <t xml:space="preserve">100025702</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>398</v>
+        <v>29942</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233782</t>
+          <t xml:space="preserve">311234962</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27A</t>
+          <t xml:space="preserve">Skellet 27C</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3506,15 +3506,15 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>476</v>
+        <v>1915</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233769</t>
+          <t xml:space="preserve">311236260</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vodroffsvej 46</t>
+          <t xml:space="preserve">Edisonsvej 3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027252</t>
+          <t xml:space="preserve">100025577</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J48">
-        <v>1486</v>
+        <v>525</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234441</t>
+          <t xml:space="preserve">311247695</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 31</t>
+          <t xml:space="preserve">Ingemannsvej 21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1964</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025702</t>
+          <t xml:space="preserve">100026391</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>29942</v>
+        <v>1000</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234962</t>
+          <t xml:space="preserve">311248626</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosegårdsvej 10</t>
+          <t xml:space="preserve">Søndre Fasanvej 40</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1967</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026430</t>
+          <t xml:space="preserve">100028380</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="J50">
-        <v>446</v>
+        <v>1699</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235357</t>
+          <t xml:space="preserve">311248632</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27C</t>
+          <t xml:space="preserve">Bülowsvej 20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100026777</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>1915</v>
+        <v>454</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236260</t>
+          <t xml:space="preserve">311248790</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,30 +3866,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 3</t>
+          <t xml:space="preserve">Storm Petersens Vej 4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025577</t>
+          <t xml:space="preserve">100047577</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J52">
-        <v>525</v>
+        <v>2679</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247695</t>
+          <t xml:space="preserve">311256544</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-16</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,40 +3941,40 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingemannsvej 21</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1964</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026391</t>
+          <t xml:space="preserve">100030861, 100227750, 100227751</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J53">
-        <v>1000</v>
+        <v>6331</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248626</t>
+          <t xml:space="preserve">311268443</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-08-24</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Fasanvej 40</t>
+          <t xml:space="preserve">Mariendalsvej 21A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028380</t>
+          <t xml:space="preserve">100028065</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="J54">
-        <v>1699</v>
+        <v>1008</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248632</t>
+          <t xml:space="preserve">311269303</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-08-29</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 20</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026777</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,21 +4110,21 @@
         </is>
       </c>
       <c r="J55">
-        <v>454</v>
+        <v>825</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248790</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,40 +4166,40 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 4</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047577</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J56">
-        <v>2679</v>
+        <v>439</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256544</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,40 +4241,40 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861, 100227750, 100227751</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J57">
-        <v>6331</v>
+        <v>464</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268443</t>
+          <t xml:space="preserve">311285951</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-24</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,40 +4316,40 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariendalsvej 21A</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028065</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J58">
-        <v>1008</v>
+        <v>371</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269303</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-29</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,17 +4391,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Dirch Passers Allé 8A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029781</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,21 +4410,21 @@
         </is>
       </c>
       <c r="J59">
-        <v>825</v>
+        <v>3880</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311293188</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,40 +4466,40 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Helgesvej 29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100026188</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>439</v>
+        <v>6682</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311373826</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2029-04-30</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,40 +4541,40 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Nyelandsvej 68</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029713</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>464</v>
+        <v>386</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285951</t>
+          <t xml:space="preserve">311379731</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,40 +4616,40 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Nyelandsvej 68</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029713</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J62">
-        <v>371</v>
+        <v>443</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311379734</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirch Passers Allé 8A</t>
+          <t xml:space="preserve">Nyelandsvej 70</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029781</t>
+          <t xml:space="preserve">100029712</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,21 +4710,21 @@
         </is>
       </c>
       <c r="J63">
-        <v>3880</v>
+        <v>311</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293188</t>
+          <t xml:space="preserve">311379735</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 29</t>
+          <t xml:space="preserve">Nyelandsvej 72</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026188</t>
+          <t xml:space="preserve">100029711</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>6682</v>
+        <v>542</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373826</t>
+          <t xml:space="preserve">311379737</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-30</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 68</t>
+          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029713</t>
+          <t xml:space="preserve">100028525</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>386</v>
+        <v>791</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379731</t>
+          <t xml:space="preserve">311381894</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-12</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 68</t>
+          <t xml:space="preserve">Prins Constantins Vej 3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,20 +4926,20 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029713</t>
+          <t xml:space="preserve">100028103</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>443</v>
+        <v>300</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379734</t>
+          <t xml:space="preserve">311384296</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 70</t>
+          <t xml:space="preserve">Ewaldsensvej 3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029712</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J67">
-        <v>311</v>
+        <v>1223</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379735</t>
+          <t xml:space="preserve">311398345</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-09-13</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,40 +5066,40 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 72</t>
+          <t xml:space="preserve">Danasvej 30B</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1910</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029711</t>
+          <t xml:space="preserve">187004</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J68">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379737</t>
+          <t xml:space="preserve">311411203</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-11-27</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,40 +5141,40 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
+          <t xml:space="preserve">Svend Trøsts Vej 19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1912</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028525</t>
+          <t xml:space="preserve">187004</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J69">
-        <v>791</v>
+        <v>440</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381894</t>
+          <t xml:space="preserve">311411203</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-12</t>
+          <t xml:space="preserve">2029-11-27</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,40 +5216,40 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prins Constantins Vej 3</t>
+          <t xml:space="preserve">Fuglevangsvej 8A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028103</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J70">
-        <v>300</v>
+        <v>842</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384296</t>
+          <t xml:space="preserve">311459962</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2030-09-09</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ewaldsensvej 3</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,30 +5301,30 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100030861</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>1223</v>
+        <v>3418</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311398345</t>
+          <t xml:space="preserve">311506322</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-13</t>
+          <t xml:space="preserve">2031-03-24</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,40 +5366,40 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danasvej 30B</t>
+          <t xml:space="preserve">Filippavej 2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910</t>
+          <t xml:space="preserve">1928</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">187004</t>
+          <t xml:space="preserve">100027259</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J72">
-        <v>586</v>
+        <v>3232</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411203</t>
+          <t xml:space="preserve">311510299</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-27</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,40 +5441,40 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svend Trøsts Vej 19</t>
+          <t xml:space="preserve">Filippavej 5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912</t>
+          <t xml:space="preserve">1928</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">187004</t>
+          <t xml:space="preserve">100027255</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J73">
-        <v>440</v>
+        <v>651</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411203</t>
+          <t xml:space="preserve">311511329</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-27</t>
+          <t xml:space="preserve">2031-04-10</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,40 +5516,40 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8A</t>
+          <t xml:space="preserve">Frydendalsvej 13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100029030</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>842</v>
+        <v>568</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459866</t>
+          <t xml:space="preserve">311607220</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-09</t>
+          <t xml:space="preserve">2032-06-13</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
+          <t xml:space="preserve">Solbjerg Have 7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,30 +5601,30 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861</t>
+          <t xml:space="preserve">174850</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J75">
-        <v>3418</v>
+        <v>7906</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506322</t>
+          <t xml:space="preserve">311655735</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-24</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,40 +5666,40 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 2</t>
+          <t xml:space="preserve">Solbjerg Have 8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027259</t>
+          <t xml:space="preserve">174851</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J76">
-        <v>3232</v>
+        <v>426</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510299</t>
+          <t xml:space="preserve">311655850</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 5</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027255</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="J77">
-        <v>651</v>
+        <v>1016</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511329</t>
+          <t xml:space="preserve">311712714</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-10</t>
+          <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 13</t>
+          <t xml:space="preserve">Sønderjyllands Alle 4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029030</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>568</v>
+        <v>4298</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311607220</t>
+          <t xml:space="preserve">311715946</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-13</t>
+          <t xml:space="preserve">2033-10-18</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,40 +5891,40 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 7</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">174850</t>
+          <t xml:space="preserve">100026659</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J79">
-        <v>7906</v>
+        <v>474</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655735</t>
+          <t xml:space="preserve">311718502</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,40 +5966,40 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 8</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">174851</t>
+          <t xml:space="preserve">100026659</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
-        <v>426</v>
+        <v>1407</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655850</t>
+          <t xml:space="preserve">311718497</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">Hoffmeyersvej 32</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100029488</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J81">
-        <v>1016</v>
+        <v>1679</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712714</t>
+          <t xml:space="preserve">311718499</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-05</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,17 +6116,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 4</t>
+          <t xml:space="preserve">Dr. Priemes Vej 3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1854</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100025651</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>4298</v>
+        <v>1434</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715946</t>
+          <t xml:space="preserve">311718872</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-18</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
+          <t xml:space="preserve">Falkoner Plads 3</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026659</t>
+          <t xml:space="preserve">100027661</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>474</v>
+        <v>5014</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718502</t>
+          <t xml:space="preserve">311718833</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
+          <t xml:space="preserve">Falkoner Plads 3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026659</t>
+          <t xml:space="preserve">100027661</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6285,11 +6285,11 @@
         </is>
       </c>
       <c r="J84">
-        <v>1407</v>
+        <v>1518</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718497</t>
+          <t xml:space="preserve">311718915</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,30 +6341,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 32</t>
+          <t xml:space="preserve">Amicisvej 11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029488</t>
+          <t xml:space="preserve">100025654</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>1679</v>
+        <v>390</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718499</t>
+          <t xml:space="preserve">311719926</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,30 +6416,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Priemes Vej 3</t>
+          <t xml:space="preserve">Bülowsvej 34B</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025651</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J86">
-        <v>1434</v>
+        <v>2018</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718872</t>
+          <t xml:space="preserve">311719910</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Plads 3</t>
+          <t xml:space="preserve">Godthåbsvej 33</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027661</t>
+          <t xml:space="preserve">100026193</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,11 +6510,11 @@
         </is>
       </c>
       <c r="J87">
-        <v>5014</v>
+        <v>345</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718833</t>
+          <t xml:space="preserve">311719933</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,30 +6566,30 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Plads 3</t>
+          <t xml:space="preserve">Hollændervej 1</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027661</t>
+          <t xml:space="preserve">100025653</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J88">
-        <v>1518</v>
+        <v>298</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718915</t>
+          <t xml:space="preserve">311719925</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 11</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025654</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,11 +6660,11 @@
         </is>
       </c>
       <c r="J89">
-        <v>390</v>
+        <v>2280</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719926</t>
+          <t xml:space="preserve">311719943</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 34B</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J90">
-        <v>2018</v>
+        <v>910</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719910</t>
+          <t xml:space="preserve">311719927</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6791,30 +6791,30 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 33</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026193</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J91">
-        <v>345</v>
+        <v>892</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719933</t>
+          <t xml:space="preserve">311719941</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 1</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025653</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J92">
-        <v>298</v>
+        <v>1827</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719925</t>
+          <t xml:space="preserve">311719948</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Hortensiavej 3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100025625</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J93">
-        <v>2280</v>
+        <v>575</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719943</t>
+          <t xml:space="preserve">311719924</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7016,30 +7016,30 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Edisonsvej 10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100025625</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>910</v>
+        <v>1906</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719927</t>
+          <t xml:space="preserve">311720841</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-08</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,30 +7091,30 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Bille Brahes Vej 2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100026838</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J95">
-        <v>892</v>
+        <v>1898</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719941</t>
+          <t xml:space="preserve">311722042</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-14</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,30 +7166,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Stockflethsvej 4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100029709</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J96">
-        <v>1827</v>
+        <v>2652</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719948</t>
+          <t xml:space="preserve">311721928</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-14</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 3</t>
+          <t xml:space="preserve">Nyelandsvej 23B</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025625</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J97">
-        <v>575</v>
+        <v>1381</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719924</t>
+          <t xml:space="preserve">311722638</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 10</t>
+          <t xml:space="preserve">Rolighedsvej 29A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">1958</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025625</t>
+          <t xml:space="preserve">100027933</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>1906</v>
+        <v>809</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720841</t>
+          <t xml:space="preserve">311722651</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-08</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,17 +7391,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bille Brahes Vej 2</t>
+          <t xml:space="preserve">Nyelandsvej 75B</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026838</t>
+          <t xml:space="preserve">100029476</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,11 +7410,11 @@
         </is>
       </c>
       <c r="J99">
-        <v>1898</v>
+        <v>2174</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722042</t>
+          <t xml:space="preserve">311723087</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-14</t>
+          <t xml:space="preserve">2033-11-17</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 4</t>
+          <t xml:space="preserve">Roskildevej 54</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,20 +7476,20 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029709</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J100">
-        <v>2652</v>
+        <v>348</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721928</t>
+          <t xml:space="preserve">311723090</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-14</t>
+          <t xml:space="preserve">2033-11-17</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23B</t>
+          <t xml:space="preserve">Howitzvej 28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100027660</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>1381</v>
+        <v>6723</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722638</t>
+          <t xml:space="preserve">311723274</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-19</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 29A</t>
+          <t xml:space="preserve">Bentzonsvej 49</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027933</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J102">
-        <v>809</v>
+        <v>941</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722651</t>
+          <t xml:space="preserve">311723412</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75B</t>
+          <t xml:space="preserve">Howitzvej 5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029476</t>
+          <t xml:space="preserve">100027640</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>2174</v>
+        <v>2139</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723087</t>
+          <t xml:space="preserve">311723408</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54</t>
+          <t xml:space="preserve">Duevej 51A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,30 +7776,30 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J104">
-        <v>348</v>
+        <v>1142</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723090</t>
+          <t xml:space="preserve">311723677</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 28</t>
+          <t xml:space="preserve">Lollandsvej 40</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027660</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>6723</v>
+        <v>2331</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723274</t>
+          <t xml:space="preserve">311723961</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-19</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bentzonsvej 49</t>
+          <t xml:space="preserve">Troels-Lunds Vej 25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100029493</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J106">
-        <v>941</v>
+        <v>4192</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723412</t>
+          <t xml:space="preserve">311723974</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 5</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027640</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J107">
-        <v>2139</v>
+        <v>4063</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723408</t>
+          <t xml:space="preserve">311723983</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,40 +8066,40 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 51A</t>
+          <t xml:space="preserve">Fuglevangsvej 5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J108">
-        <v>1142</v>
+        <v>2396</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723677</t>
+          <t xml:space="preserve">311723989</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,30 +8141,30 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lollandsvej 40</t>
+          <t xml:space="preserve">Fuglevangsvej 8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J109">
-        <v>2331</v>
+        <v>2235</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723961</t>
+          <t xml:space="preserve">311723988</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troels-Lunds Vej 25</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029493</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J110">
-        <v>4192</v>
+        <v>3767</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723974</t>
+          <t xml:space="preserve">311723998</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
+          <t xml:space="preserve">Duevej 53A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J111">
-        <v>4063</v>
+        <v>1859</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723983</t>
+          <t xml:space="preserve">311724465</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 5</t>
+          <t xml:space="preserve">Tesdorpfsvej 19</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100029716</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>2396</v>
+        <v>1897</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723989</t>
+          <t xml:space="preserve">311725944</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,30 +8441,30 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>2235</v>
+        <v>7469</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723988</t>
+          <t xml:space="preserve">311726343</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J114">
-        <v>3767</v>
+        <v>1826</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723998</t>
+          <t xml:space="preserve">311726342</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 53A</t>
+          <t xml:space="preserve">Carl Plougs Vej 4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1913</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100027175</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
-        <v>1859</v>
+        <v>1283</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724465</t>
+          <t xml:space="preserve">311726476</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-23</t>
+          <t xml:space="preserve">2033-12-03</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 19</t>
+          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029716</t>
+          <t xml:space="preserve">100027175</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>1897</v>
+        <v>5031</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725944</t>
+          <t xml:space="preserve">311726475</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2033-12-03</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>7469</v>
+        <v>2221</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726343</t>
+          <t xml:space="preserve">311726873</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,30 +8816,30 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Grundtvigsvej 9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1864</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100026309</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J118">
-        <v>1826</v>
+        <v>10865</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726342</t>
+          <t xml:space="preserve">311727265</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Plougs Vej 4</t>
+          <t xml:space="preserve">La Cours Vej 2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027175</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>1283</v>
+        <v>5199</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726476</t>
+          <t xml:space="preserve">311727254</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-03</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
+          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027175</t>
+          <t xml:space="preserve">100029769</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,11 +8985,11 @@
         </is>
       </c>
       <c r="J120">
-        <v>5031</v>
+        <v>1176</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726475</t>
+          <t xml:space="preserve">311733387</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-03</t>
+          <t xml:space="preserve">2034-01-16</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">Pile Alle 33</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">191032, 191033</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J121">
-        <v>2221</v>
+        <v>1248</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726873</t>
+          <t xml:space="preserve">311733392</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-05</t>
+          <t xml:space="preserve">2034-01-16</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,17 +9116,17 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigsvej 9</t>
+          <t xml:space="preserve">Finsensvej 92</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026309</t>
+          <t xml:space="preserve">100029806</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>10865</v>
+        <v>3370</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727265</t>
+          <t xml:space="preserve">311734724</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2034-01-20</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Cours Vej 2</t>
+          <t xml:space="preserve">Falkoner Alle 130</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100028184</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>5199</v>
+        <v>562</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727254</t>
+          <t xml:space="preserve">311735174</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2034-01-25</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
+          <t xml:space="preserve">Falkonergårdsvej 21</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029769</t>
+          <t xml:space="preserve">100028183</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>1176</v>
+        <v>375</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733387</t>
+          <t xml:space="preserve">311735114</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-16</t>
+          <t xml:space="preserve">2034-01-25</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pile Alle 33</t>
+          <t xml:space="preserve">Sofus Francks Vænge 28</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">191032, 191033</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>1248</v>
+        <v>856</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733392</t>
+          <t xml:space="preserve">311742694</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-16</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finsensvej 92</t>
+          <t xml:space="preserve">Sofus Francks Vænge 30</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029806</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,11 +9435,11 @@
         </is>
       </c>
       <c r="J126">
-        <v>3370</v>
+        <v>6815</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734724</t>
+          <t xml:space="preserve">311742695</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-20</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Alle 130</t>
+          <t xml:space="preserve">Sofus Francks Vænge 34</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028184</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J127">
-        <v>562</v>
+        <v>706</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735174</t>
+          <t xml:space="preserve">311742696</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-25</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,30 +9566,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkonergårdsvej 21</t>
+          <t xml:space="preserve">Christian Paulsens Vej 26</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028183</t>
+          <t xml:space="preserve">100029283</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J128">
-        <v>375</v>
+        <v>2340</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735114</t>
+          <t xml:space="preserve">311736719</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-25</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 28</t>
+          <t xml:space="preserve">Godthåbsvej 21A</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9651,20 +9651,20 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>856</v>
+        <v>812</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742694</t>
+          <t xml:space="preserve">311736735</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 30</t>
+          <t xml:space="preserve">Godthåbsvej 23</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J130">
-        <v>6815</v>
+        <v>1290</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742695</t>
+          <t xml:space="preserve">311736733</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 34</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100029324</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>706</v>
+        <v>2412</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742696</t>
+          <t xml:space="preserve">311736741</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 26</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029283</t>
+          <t xml:space="preserve">100029349</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>2340</v>
+        <v>2532</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736719</t>
+          <t xml:space="preserve">311737441</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 21A</t>
+          <t xml:space="preserve">Nyelandsvej 25B</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J133">
-        <v>812</v>
+        <v>467</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736735</t>
+          <t xml:space="preserve">311738410</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 23</t>
+          <t xml:space="preserve">Roskildevej 54A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J134">
-        <v>1290</v>
+        <v>382</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736733</t>
+          <t xml:space="preserve">311738404</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
+          <t xml:space="preserve">Roskildevej 54A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029324</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J135">
-        <v>2412</v>
+        <v>759</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736741</t>
+          <t xml:space="preserve">311738403</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
+          <t xml:space="preserve">Lyøvej 12</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029349</t>
+          <t xml:space="preserve">100025884</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>2532</v>
+        <v>654</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737441</t>
+          <t xml:space="preserve">311738624</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25B</t>
+          <t xml:space="preserve">Nyelandsvej 25A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10256,15 +10256,15 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J137">
-        <v>467</v>
+        <v>1086</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738410</t>
+          <t xml:space="preserve">311738883</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54A</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,20 +10326,20 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100029465</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>382</v>
+        <v>458</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738404</t>
+          <t xml:space="preserve">311740954</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54A</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100029465</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J139">
-        <v>759</v>
+        <v>4137</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738403</t>
+          <t xml:space="preserve">311739450</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyøvej 12</t>
+          <t xml:space="preserve">Nyelandsvej 51</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025884</t>
+          <t xml:space="preserve">100025875</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="J140">
-        <v>654</v>
+        <v>541</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738624</t>
+          <t xml:space="preserve">311739362</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-13</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25A</t>
+          <t xml:space="preserve">Nyelandsvej 75</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029459</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>1086</v>
+        <v>1009</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738883</t>
+          <t xml:space="preserve">311739367</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-14</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,17 +10616,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
+          <t xml:space="preserve">Sankt Knuds Vej 32</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029465</t>
+          <t xml:space="preserve">100027037</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>458</v>
+        <v>846</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740954</t>
+          <t xml:space="preserve">311739928</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,20 +10701,20 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029465</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J143">
-        <v>4137</v>
+        <v>594</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739450</t>
+          <t xml:space="preserve">311740966</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-26</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 51</t>
+          <t xml:space="preserve">Rosenørns Alle 59</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1970</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025875</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J144">
-        <v>541</v>
+        <v>1965</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739362</t>
+          <t xml:space="preserve">311741888</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75</t>
+          <t xml:space="preserve">Svanholmsvej 15</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1905</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029459</t>
+          <t xml:space="preserve">100027101</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>1009</v>
+        <v>1287</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739367</t>
+          <t xml:space="preserve">311741757</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 32</t>
+          <t xml:space="preserve">Vagtelvej 58</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027037</t>
+          <t xml:space="preserve">100027314</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>846</v>
+        <v>1134</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739928</t>
+          <t xml:space="preserve">311741762</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-20</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">Eversvej 2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,20 +11001,20 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100029822</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>594</v>
+        <v>9353</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740966</t>
+          <t xml:space="preserve">311743570</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-26</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenørns Alle 59</t>
+          <t xml:space="preserve">Tesdorpfsvej 23</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100029708</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>1965</v>
+        <v>291</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741888</t>
+          <t xml:space="preserve">311742345</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanholmsvej 15</t>
+          <t xml:space="preserve">Tesdorpfsvej 25</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027101</t>
+          <t xml:space="preserve">100029707</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>1287</v>
+        <v>1491</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741757</t>
+          <t xml:space="preserve">311742340</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vagtelvej 58</t>
+          <t xml:space="preserve">Nimbusparken 26</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027314</t>
+          <t xml:space="preserve">100029646</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>1134</v>
+        <v>5305</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741762</t>
+          <t xml:space="preserve">311743895</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eversvej 2</t>
+          <t xml:space="preserve">Virginiavej 11</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029822</t>
+          <t xml:space="preserve">100026985</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>9353</v>
+        <v>814</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743570</t>
+          <t xml:space="preserve">311743940</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 23</t>
+          <t xml:space="preserve">Flintholm Alle 25</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029708</t>
+          <t xml:space="preserve">100029803</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>291</v>
+        <v>3250</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742345</t>
+          <t xml:space="preserve">311744589</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 25</t>
+          <t xml:space="preserve">Flintholm Alle 35</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029707</t>
+          <t xml:space="preserve">100029802</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11460,11 +11460,11 @@
         </is>
       </c>
       <c r="J153">
-        <v>1491</v>
+        <v>3280</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742340</t>
+          <t xml:space="preserve">311744599</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nimbusparken 26</t>
+          <t xml:space="preserve">Flintholm Alle 45</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029646</t>
+          <t xml:space="preserve">100029790</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>5305</v>
+        <v>2615</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743895</t>
+          <t xml:space="preserve">311744608</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virginiavej 11</t>
+          <t xml:space="preserve">Christian Paulsens Vej 32</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026985</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J155">
-        <v>814</v>
+        <v>2505</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743940</t>
+          <t xml:space="preserve">311745373</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 25</t>
+          <t xml:space="preserve">Elga Olgas Vej 5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029803</t>
+          <t xml:space="preserve">100029824</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>3250</v>
+        <v>4407</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744589</t>
+          <t xml:space="preserve">311745450</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11736,22 +11736,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 35</t>
+          <t xml:space="preserve">Lynge Bygade 60</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3540</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029802</t>
+          <t xml:space="preserve">2252337</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>3280</v>
+        <v>534</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744599</t>
+          <t xml:space="preserve">311745449</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 45</t>
+          <t xml:space="preserve">Sønderjyllands Alle 10</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029790</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>2615</v>
+        <v>3120</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744608</t>
+          <t xml:space="preserve">311767998</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 32</t>
+          <t xml:space="preserve">Nyelandsvej 85</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,30 +11901,30 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">100029472</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>2505</v>
+        <v>4687</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745373</t>
+          <t xml:space="preserve">311746471</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Norca ApS</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-03-19</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elga Olgas Vej 5</t>
+          <t xml:space="preserve">Godthåbsvej 83</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029824</t>
+          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>4407</v>
+        <v>13136</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745450</t>
+          <t xml:space="preserve">311746996</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12036,22 +12036,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynge Bygade 60</t>
+          <t xml:space="preserve">Frederiksvej 51</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2252337</t>
+          <t xml:space="preserve">100029085</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>534</v>
+        <v>2080</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745449</t>
+          <t xml:space="preserve">311758493</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 10</t>
+          <t xml:space="preserve">Nordre Fasanvej 81</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">100029721</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>3120</v>
+        <v>787</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767998</t>
+          <t xml:space="preserve">311758487</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 85</t>
+          <t xml:space="preserve">Beringsvej 8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029472</t>
+          <t xml:space="preserve">100030255</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,21 +12210,21 @@
         </is>
       </c>
       <c r="J163">
-        <v>4687</v>
+        <v>413</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746471</t>
+          <t xml:space="preserve">311926722</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca ApS</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-19</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 83</t>
+          <t xml:space="preserve">Hoffmeyersvej 40</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
+          <t xml:space="preserve">100029487</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,21 +12285,21 @@
         </is>
       </c>
       <c r="J164">
-        <v>13136</v>
+        <v>1071</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746996</t>
+          <t xml:space="preserve">311928517</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-21</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksvej 51</t>
+          <t xml:space="preserve">Nordre Fasanvej 75</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029085</t>
+          <t xml:space="preserve">100029720</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,21 +12360,21 @@
         </is>
       </c>
       <c r="J165">
-        <v>2080</v>
+        <v>1334</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758493</t>
+          <t xml:space="preserve">311928590</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,17 +12416,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 81</t>
+          <t xml:space="preserve">Svanemosegårdsvej 10</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1967</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029721</t>
+          <t xml:space="preserve">100026430</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,21 +12435,21 @@
         </is>
       </c>
       <c r="J166">
-        <v>787</v>
+        <v>446</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758487</t>
+          <t xml:space="preserve">311929077</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">

--- a/public/exports/11259979.xlsx
+++ b/public/exports/11259979.xlsx
@@ -1541,17 +1541,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Segelckesvej 7</t>
+          <t xml:space="preserve">Thorvaldsensvej 24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030239</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="J21">
-        <v>408</v>
+        <v>3792</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223800</t>
+          <t xml:space="preserve">311223802</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1616,17 +1616,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 24</t>
+          <t xml:space="preserve">Storm Petersens Vej 5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100047575</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1635,21 +1635,21 @@
         </is>
       </c>
       <c r="J22">
-        <v>3792</v>
+        <v>297</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223802</t>
+          <t xml:space="preserve">311225730</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-21</t>
+          <t xml:space="preserve">2027-01-31</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 5</t>
+          <t xml:space="preserve">Hortensiavej 11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047575</t>
+          <t xml:space="preserve">100025624</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1710,11 +1710,11 @@
         </is>
       </c>
       <c r="J23">
-        <v>297</v>
+        <v>440</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225730</t>
+          <t xml:space="preserve">311226748</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-31</t>
+          <t xml:space="preserve">2027-02-06</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 11</t>
+          <t xml:space="preserve">Hortensiavej 13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025624</t>
+          <t xml:space="preserve">100025599</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1785,11 +1785,11 @@
         </is>
       </c>
       <c r="J24">
-        <v>440</v>
+        <v>255</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226748</t>
+          <t xml:space="preserve">311226749</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1836,22 +1836,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">230</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 13</t>
+          <t xml:space="preserve">Biskop Svanes Vej 75</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">3460</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025599</t>
+          <t xml:space="preserve">8312706</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,21 +1860,21 @@
         </is>
       </c>
       <c r="J25">
-        <v>255</v>
+        <v>1322</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226749</t>
+          <t xml:space="preserve">311231330</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-06</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1911,22 +1911,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">230</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biskop Svanes Vej 75</t>
+          <t xml:space="preserve">Nørrevænget 14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3460</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8312706</t>
+          <t xml:space="preserve">2137707</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,11 +1935,11 @@
         </is>
       </c>
       <c r="J26">
-        <v>1322</v>
+        <v>295</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231330</t>
+          <t xml:space="preserve">311227340</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1986,22 +1986,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 14</t>
+          <t xml:space="preserve">Amicisvej 9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137707</t>
+          <t xml:space="preserve">100025655</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,21 +2010,21 @@
         </is>
       </c>
       <c r="J27">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227340</t>
+          <t xml:space="preserve">311227832</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 9</t>
+          <t xml:space="preserve">Bülowsvej 14A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025655</t>
+          <t xml:space="preserve">100026669</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2085,11 +2085,11 @@
         </is>
       </c>
       <c r="J28">
-        <v>340</v>
+        <v>626</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227832</t>
+          <t xml:space="preserve">311227831</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 14A</t>
+          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026669</t>
+          <t xml:space="preserve">100025685</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,11 +2160,11 @@
         </is>
       </c>
       <c r="J29">
-        <v>626</v>
+        <v>953</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227831</t>
+          <t xml:space="preserve">311229051</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-02-17</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksberg Bredegade 11</t>
+          <t xml:space="preserve">Frydendalsvej 19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025685</t>
+          <t xml:space="preserve">100028929</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="J30">
-        <v>953</v>
+        <v>805</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229051</t>
+          <t xml:space="preserve">311229048</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 19</t>
+          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">1904</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028929</t>
+          <t xml:space="preserve">100027090</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,21 +2310,21 @@
         </is>
       </c>
       <c r="J31">
-        <v>805</v>
+        <v>589</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229048</t>
+          <t xml:space="preserve">311230550</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Midtjylland</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-17</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2366,30 +2366,30 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Forhåbningsholms Alle 24</t>
+          <t xml:space="preserve">Junggreensvej 12B</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1904</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027090</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J32">
-        <v>589</v>
+        <v>1152</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230550</t>
+          <t xml:space="preserve">311230598</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junggreensvej 12B</t>
+          <t xml:space="preserve">N.J. Fjords Alle 15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1957</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100026522</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J33">
-        <v>1152</v>
+        <v>300</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230598</t>
+          <t xml:space="preserve">311230618</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 15</t>
+          <t xml:space="preserve">N.J. Fjords Alle 17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2531,11 +2531,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J34">
-        <v>300</v>
+        <v>376</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,30 +2591,30 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">N.J. Fjords Alle 17</t>
+          <t xml:space="preserve">Nyelandsvej 66</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1957</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026522</t>
+          <t xml:space="preserve">100029714</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230618</t>
+          <t xml:space="preserve">311230609</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 66</t>
+          <t xml:space="preserve">Sankt Knuds Vej 7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029714</t>
+          <t xml:space="preserve">100026917</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,11 +2685,11 @@
         </is>
       </c>
       <c r="J36">
-        <v>342</v>
+        <v>433</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230609</t>
+          <t xml:space="preserve">311230540</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 7</t>
+          <t xml:space="preserve">Bakkegårds Alle 18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">1804</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026917</t>
+          <t xml:space="preserve">191034</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,11 +2760,11 @@
         </is>
       </c>
       <c r="J37">
-        <v>433</v>
+        <v>1225</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230540</t>
+          <t xml:space="preserve">311230651</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkegårds Alle 18</t>
+          <t xml:space="preserve">Dronning Olgas Vej 6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">191034</t>
+          <t xml:space="preserve">100028120</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="J38">
-        <v>1225</v>
+        <v>580</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230651</t>
+          <t xml:space="preserve">311230652</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Olgas Vej 6</t>
+          <t xml:space="preserve">Rahbeks Alle 19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1801</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028120</t>
+          <t xml:space="preserve">100028743</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>580</v>
+        <v>388</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230652</t>
+          <t xml:space="preserve">311231234</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-28</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahbeks Alle 19</t>
+          <t xml:space="preserve">Skærbygårdsvej 15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028743</t>
+          <t xml:space="preserve">5347084</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J40">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231234</t>
+          <t xml:space="preserve">311231683</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-28</t>
+          <t xml:space="preserve">2027-03-02</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3036,35 +3036,35 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skærbygårdsvej 15</t>
+          <t xml:space="preserve">Thorvaldsensvej 26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">1871</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5347084</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J41">
-        <v>1209</v>
+        <v>422</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231683</t>
+          <t xml:space="preserve">311233222</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-02</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3111,35 +3111,35 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">306</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorvaldsensvej 26</t>
+          <t xml:space="preserve">Oddenvej 90B</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871</t>
+          <t xml:space="preserve">4500</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">2428914</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J42">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233222</t>
+          <t xml:space="preserve">311233782</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-13</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3186,35 +3186,35 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">306</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oddenvej 90B</t>
+          <t xml:space="preserve">Skellet 27A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2428914</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J43">
-        <v>398</v>
+        <v>476</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233782</t>
+          <t xml:space="preserve">311233769</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3266,30 +3266,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27A</t>
+          <t xml:space="preserve">Vodroffsvej 46</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1900</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100027252</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>476</v>
+        <v>1486</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233769</t>
+          <t xml:space="preserve">311234441</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-13</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vodroffsvej 46</t>
+          <t xml:space="preserve">Allegade 31</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027252</t>
+          <t xml:space="preserve">100025702</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>1486</v>
+        <v>29942</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234441</t>
+          <t xml:space="preserve">311234962</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 31</t>
+          <t xml:space="preserve">Skellet 27C</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025702</t>
+          <t xml:space="preserve">100029530</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3435,11 +3435,11 @@
         </is>
       </c>
       <c r="J46">
-        <v>29942</v>
+        <v>1915</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234962</t>
+          <t xml:space="preserve">311236260</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2027-03-23</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,30 +3491,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skellet 27C</t>
+          <t xml:space="preserve">Edisonsvej 3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029530</t>
+          <t xml:space="preserve">100025577</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J47">
-        <v>1915</v>
+        <v>525</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236260</t>
+          <t xml:space="preserve">311247695</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-23</t>
+          <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 3</t>
+          <t xml:space="preserve">Ingemannsvej 21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">1964</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025577</t>
+          <t xml:space="preserve">100026391</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>525</v>
+        <v>1000</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247695</t>
+          <t xml:space="preserve">311248626</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-16</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingemannsvej 21</t>
+          <t xml:space="preserve">Søndre Fasanvej 40</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1964</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026391</t>
+          <t xml:space="preserve">100028380</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,16 +3660,16 @@
         </is>
       </c>
       <c r="J49">
-        <v>1000</v>
+        <v>1699</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248626</t>
+          <t xml:space="preserve">311248632</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Fasanvej 40</t>
+          <t xml:space="preserve">Bülowsvej 20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028380</t>
+          <t xml:space="preserve">100026777</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,21 +3735,21 @@
         </is>
       </c>
       <c r="J50">
-        <v>1699</v>
+        <v>454</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248632</t>
+          <t xml:space="preserve">311248790</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 20</t>
+          <t xml:space="preserve">Storm Petersens Vej 4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026777</t>
+          <t xml:space="preserve">100047577</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>454</v>
+        <v>2679</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248790</t>
+          <t xml:space="preserve">311256544</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storm Petersens Vej 4</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3876,30 +3876,30 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047577</t>
+          <t xml:space="preserve">100030861, 100227750, 100227751</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J52">
-        <v>2679</v>
+        <v>6331</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256544</t>
+          <t xml:space="preserve">311268443</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-08-24</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 41A</t>
+          <t xml:space="preserve">Mariendalsvej 21A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,30 +3951,30 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861, 100227750, 100227751</t>
+          <t xml:space="preserve">100028065</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J53">
-        <v>6331</v>
+        <v>1008</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268443</t>
+          <t xml:space="preserve">311269303</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-24</t>
+          <t xml:space="preserve">2027-08-29</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariendalsvej 21A</t>
+          <t xml:space="preserve">Steenwinkelsvej 19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1966</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028065</t>
+          <t xml:space="preserve">100026399</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="J54">
-        <v>1008</v>
+        <v>825</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269303</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Oluf Jørgensen A/S</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-29</t>
+          <t xml:space="preserve">2027-11-27</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4106,11 +4106,11 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J55">
-        <v>825</v>
+        <v>439</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4181,15 +4181,15 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J56">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311285951</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4256,15 +4256,15 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J57">
-        <v>464</v>
+        <v>371</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285951</t>
+          <t xml:space="preserve">311285953</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4316,40 +4316,40 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steenwinkelsvej 19</t>
+          <t xml:space="preserve">Dirch Passers Allé 8A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026399</t>
+          <t xml:space="preserve">100029781</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>371</v>
+        <v>3880</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285953</t>
+          <t xml:space="preserve">311293188</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oluf Jørgensen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-27</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirch Passers Allé 8A</t>
+          <t xml:space="preserve">Helgesvej 29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029781</t>
+          <t xml:space="preserve">100026188</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,21 +4410,21 @@
         </is>
       </c>
       <c r="J59">
-        <v>3880</v>
+        <v>6682</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293188</t>
+          <t xml:space="preserve">311373826</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2029-04-30</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helgesvej 29</t>
+          <t xml:space="preserve">Nyelandsvej 68</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026188</t>
+          <t xml:space="preserve">100029713</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="J60">
-        <v>6682</v>
+        <v>386</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373826</t>
+          <t xml:space="preserve">311379731</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-30</t>
+          <t xml:space="preserve">2029-05-29</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4556,15 +4556,15 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J61">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379731</t>
+          <t xml:space="preserve">311379734</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 68</t>
+          <t xml:space="preserve">Nyelandsvej 70</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029713</t>
+          <t xml:space="preserve">100029712</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>443</v>
+        <v>311</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379734</t>
+          <t xml:space="preserve">311379735</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 70</t>
+          <t xml:space="preserve">Nyelandsvej 72</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029712</t>
+          <t xml:space="preserve">100029711</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>311</v>
+        <v>542</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379735</t>
+          <t xml:space="preserve">311379737</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 72</t>
+          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029711</t>
+          <t xml:space="preserve">100028525</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>542</v>
+        <v>791</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379737</t>
+          <t xml:space="preserve">311381894</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-29</t>
+          <t xml:space="preserve">2029-06-12</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmester Fischers Vej 9</t>
+          <t xml:space="preserve">Prins Constantins Vej 3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028525</t>
+          <t xml:space="preserve">100028103</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>791</v>
+        <v>300</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381894</t>
+          <t xml:space="preserve">311384296</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-12</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prins Constantins Vej 3</t>
+          <t xml:space="preserve">Ewaldsensvej 3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,20 +4926,20 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028103</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J66">
-        <v>300</v>
+        <v>1223</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384296</t>
+          <t xml:space="preserve">311398345</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2029-09-13</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,40 +4991,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ewaldsensvej 3</t>
+          <t xml:space="preserve">Danasvej 30B</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1910</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">187004</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J67">
-        <v>1223</v>
+        <v>586</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311398345</t>
+          <t xml:space="preserve">311411203</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-09-13</t>
+          <t xml:space="preserve">2029-11-27</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danasvej 30B</t>
+          <t xml:space="preserve">Svend Trøsts Vej 19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910</t>
+          <t xml:space="preserve">1912</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J68">
-        <v>586</v>
+        <v>440</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,40 +5141,40 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svend Trøsts Vej 19</t>
+          <t xml:space="preserve">Fuglevangsvej 8A</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">187004</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J69">
-        <v>440</v>
+        <v>842</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411203</t>
+          <t xml:space="preserve">311459962</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-27</t>
+          <t xml:space="preserve">2030-09-09</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,40 +5216,40 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8A</t>
+          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100030861</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>842</v>
+        <v>3418</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311459962</t>
+          <t xml:space="preserve">311506322</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-09</t>
+          <t xml:space="preserve">2031-03-24</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernhard Bangs Alle 43</t>
+          <t xml:space="preserve">Filippavej 2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1928</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030861</t>
+          <t xml:space="preserve">100027259</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,11 +5310,11 @@
         </is>
       </c>
       <c r="J71">
-        <v>3418</v>
+        <v>3232</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311506322</t>
+          <t xml:space="preserve">311510299</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-24</t>
+          <t xml:space="preserve">2031-04-07</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 2</t>
+          <t xml:space="preserve">Filippavej 5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027259</t>
+          <t xml:space="preserve">100027255</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>3232</v>
+        <v>651</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311510299</t>
+          <t xml:space="preserve">311511329</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-07</t>
+          <t xml:space="preserve">2031-04-10</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filippavej 5</t>
+          <t xml:space="preserve">Frydendalsvej 13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027255</t>
+          <t xml:space="preserve">100029030</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="J73">
-        <v>651</v>
+        <v>568</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511329</t>
+          <t xml:space="preserve">311607220</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-10</t>
+          <t xml:space="preserve">2032-06-13</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,40 +5516,40 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frydendalsvej 13</t>
+          <t xml:space="preserve">Solbjerg Have 7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029030</t>
+          <t xml:space="preserve">174850</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J74">
-        <v>568</v>
+        <v>7906</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311607220</t>
+          <t xml:space="preserve">311655735</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-13</t>
+          <t xml:space="preserve">2033-01-24</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 7</t>
+          <t xml:space="preserve">Solbjerg Have 8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">174850</t>
+          <t xml:space="preserve">174851</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J75">
-        <v>7906</v>
+        <v>426</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655735</t>
+          <t xml:space="preserve">311655850</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerg Have 8</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,30 +5676,30 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">174851</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>426</v>
+        <v>1016</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655850</t>
+          <t xml:space="preserve">311712714</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-24</t>
+          <t xml:space="preserve">2033-10-05</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">Sønderjyllands Alle 4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100029329</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="J77">
-        <v>1016</v>
+        <v>4298</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712714</t>
+          <t xml:space="preserve">311715946</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-05</t>
+          <t xml:space="preserve">2033-10-18</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 4</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1879</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029329</t>
+          <t xml:space="preserve">100026659</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>4298</v>
+        <v>474</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715946</t>
+          <t xml:space="preserve">311718502</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-18</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19A</t>
+          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,15 +5906,15 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J79">
-        <v>474</v>
+        <v>1407</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718502</t>
+          <t xml:space="preserve">311718497</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,30 +5966,30 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Ørsteds Vej 19B</t>
+          <t xml:space="preserve">Hoffmeyersvej 32</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1879</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026659</t>
+          <t xml:space="preserve">100029488</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J80">
-        <v>1407</v>
+        <v>1679</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718497</t>
+          <t xml:space="preserve">311718499</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,30 +6041,30 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 32</t>
+          <t xml:space="preserve">Dr. Priemes Vej 3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1854</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029488</t>
+          <t xml:space="preserve">100025651</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J81">
-        <v>1679</v>
+        <v>1434</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718499</t>
+          <t xml:space="preserve">311718872</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-10-31</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,17 +6116,17 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Priemes Vej 3</t>
+          <t xml:space="preserve">Falkoner Plads 3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025651</t>
+          <t xml:space="preserve">100027661</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>1434</v>
+        <v>5014</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718872</t>
+          <t xml:space="preserve">311718833</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6206,15 +6206,15 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J83">
-        <v>5014</v>
+        <v>1518</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718833</t>
+          <t xml:space="preserve">311718915</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Plads 3</t>
+          <t xml:space="preserve">Amicisvej 11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1852</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027661</t>
+          <t xml:space="preserve">100025654</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
-        <v>1518</v>
+        <v>390</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718915</t>
+          <t xml:space="preserve">311719926</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-31</t>
+          <t xml:space="preserve">2033-11-03</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,30 +6341,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amicisvej 11</t>
+          <t xml:space="preserve">Bülowsvej 34B</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852</t>
+          <t xml:space="preserve">1870</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025654</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J85">
-        <v>390</v>
+        <v>2018</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719926</t>
+          <t xml:space="preserve">311719910</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,30 +6416,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bülowsvej 34B</t>
+          <t xml:space="preserve">Godthåbsvej 33</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100026193</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>2018</v>
+        <v>345</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719910</t>
+          <t xml:space="preserve">311719933</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 33</t>
+          <t xml:space="preserve">Hollændervej 1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1855</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026193</t>
+          <t xml:space="preserve">100025653</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,11 +6510,11 @@
         </is>
       </c>
       <c r="J87">
-        <v>345</v>
+        <v>298</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719933</t>
+          <t xml:space="preserve">311719925</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 1</t>
+          <t xml:space="preserve">Hollændervej 3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025653</t>
+          <t xml:space="preserve">100025652</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,11 +6585,11 @@
         </is>
       </c>
       <c r="J88">
-        <v>298</v>
+        <v>2280</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719925</t>
+          <t xml:space="preserve">311719943</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6656,15 +6656,15 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J89">
-        <v>2280</v>
+        <v>910</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719943</t>
+          <t xml:space="preserve">311719927</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6731,15 +6731,15 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J90">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719927</t>
+          <t xml:space="preserve">311719941</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6806,15 +6806,15 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J91">
-        <v>892</v>
+        <v>1827</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719941</t>
+          <t xml:space="preserve">311719948</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,30 +6866,30 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollændervej 3</t>
+          <t xml:space="preserve">Hortensiavej 3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855</t>
+          <t xml:space="preserve">1857</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025652</t>
+          <t xml:space="preserve">100025625</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J92">
-        <v>1827</v>
+        <v>575</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719948</t>
+          <t xml:space="preserve">311719924</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hortensiavej 3</t>
+          <t xml:space="preserve">Edisonsvej 10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1857</t>
+          <t xml:space="preserve">1856</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6956,15 +6956,15 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>575</v>
+        <v>1906</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311719924</t>
+          <t xml:space="preserve">311720841</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-03</t>
+          <t xml:space="preserve">2033-11-08</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Edisonsvej 10</t>
+          <t xml:space="preserve">Bille Brahes Vej 2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856</t>
+          <t xml:space="preserve">1963</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025625</t>
+          <t xml:space="preserve">100026838</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7035,11 +7035,11 @@
         </is>
       </c>
       <c r="J94">
-        <v>1906</v>
+        <v>1898</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311720841</t>
+          <t xml:space="preserve">311722042</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-08</t>
+          <t xml:space="preserve">2033-11-14</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,17 +7091,17 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bille Brahes Vej 2</t>
+          <t xml:space="preserve">Stockflethsvej 4</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1963</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026838</t>
+          <t xml:space="preserve">100029709</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,11 +7110,11 @@
         </is>
       </c>
       <c r="J95">
-        <v>1898</v>
+        <v>2652</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722042</t>
+          <t xml:space="preserve">311721928</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 4</t>
+          <t xml:space="preserve">Nyelandsvej 23B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,20 +7176,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029709</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J96">
-        <v>2652</v>
+        <v>1381</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721928</t>
+          <t xml:space="preserve">311722638</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-14</t>
+          <t xml:space="preserve">2033-11-16</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,30 +7241,30 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23B</t>
+          <t xml:space="preserve">Rolighedsvej 29A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1958</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100027933</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>1381</v>
+        <v>809</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722638</t>
+          <t xml:space="preserve">311722651</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 29A</t>
+          <t xml:space="preserve">Nyelandsvej 75B</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1958</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027933</t>
+          <t xml:space="preserve">100029476</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>809</v>
+        <v>2174</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722651</t>
+          <t xml:space="preserve">311723087</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-16</t>
+          <t xml:space="preserve">2033-11-17</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75B</t>
+          <t xml:space="preserve">Roskildevej 54</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,20 +7401,20 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029476</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J99">
-        <v>2174</v>
+        <v>348</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723087</t>
+          <t xml:space="preserve">311723090</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54</t>
+          <t xml:space="preserve">Howitzvej 28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,20 +7476,20 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100027660</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>348</v>
+        <v>6723</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723090</t>
+          <t xml:space="preserve">311723274</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-17</t>
+          <t xml:space="preserve">2033-11-19</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 28</t>
+          <t xml:space="preserve">Bentzonsvej 49</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027660</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J101">
-        <v>6723</v>
+        <v>941</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723274</t>
+          <t xml:space="preserve">311723412</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-19</t>
+          <t xml:space="preserve">2033-11-20</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bentzonsvej 49</t>
+          <t xml:space="preserve">Howitzvej 5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,20 +7626,20 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100027640</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>941</v>
+        <v>2139</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723412</t>
+          <t xml:space="preserve">311723408</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Howitzvej 5</t>
+          <t xml:space="preserve">Duevej 51A</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,30 +7701,30 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027640</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J103">
-        <v>2139</v>
+        <v>1142</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723408</t>
+          <t xml:space="preserve">311723677</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-20</t>
+          <t xml:space="preserve">2033-11-21</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 51A</t>
+          <t xml:space="preserve">Lollandsvej 40</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,25 +7776,25 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100026025</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>1142</v>
+        <v>2331</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723677</t>
+          <t xml:space="preserve">311723961</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lollandsvej 40</t>
+          <t xml:space="preserve">Troels-Lunds Vej 25</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026025</t>
+          <t xml:space="preserve">100029493</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>2331</v>
+        <v>4192</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723961</t>
+          <t xml:space="preserve">311723974</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troels-Lunds Vej 25</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,20 +7926,20 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029493</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J106">
-        <v>4192</v>
+        <v>4063</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723974</t>
+          <t xml:space="preserve">311723983</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-21</t>
+          <t xml:space="preserve">2033-11-22</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,30 +7991,30 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 4</t>
+          <t xml:space="preserve">Fuglevangsvej 5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1962</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J107">
-        <v>4063</v>
+        <v>2396</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723983</t>
+          <t xml:space="preserve">311723989</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 5</t>
+          <t xml:space="preserve">Fuglevangsvej 8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100026820</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J108">
-        <v>2396</v>
+        <v>2235</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723989</t>
+          <t xml:space="preserve">311723988</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 8</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026820</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>2235</v>
+        <v>3767</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723988</t>
+          <t xml:space="preserve">311723998</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">Duevej 53A</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100027673</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J110">
-        <v>3767</v>
+        <v>1859</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311723998</t>
+          <t xml:space="preserve">311724465</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-22</t>
+          <t xml:space="preserve">2033-11-23</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duevej 53A</t>
+          <t xml:space="preserve">Tesdorpfsvej 19</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027673</t>
+          <t xml:space="preserve">100029716</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>1859</v>
+        <v>1897</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311724465</t>
+          <t xml:space="preserve">311725944</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-23</t>
+          <t xml:space="preserve">2033-11-30</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 19</t>
+          <t xml:space="preserve">P.G. Ramms Alle 26</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029716</t>
+          <t xml:space="preserve">100029627</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>1897</v>
+        <v>7469</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725944</t>
+          <t xml:space="preserve">311726343</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-30</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8456,15 +8456,15 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J113">
-        <v>7469</v>
+        <v>1826</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726343</t>
+          <t xml:space="preserve">311726342</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">P.G. Ramms Alle 26</t>
+          <t xml:space="preserve">Carl Plougs Vej 4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1913</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029627</t>
+          <t xml:space="preserve">100027175</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J114">
-        <v>1826</v>
+        <v>1283</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726342</t>
+          <t xml:space="preserve">311726476</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2033-12-03</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carl Plougs Vej 4</t>
+          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913</t>
+          <t xml:space="preserve">1911</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8606,15 +8606,15 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>1283</v>
+        <v>5031</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726476</t>
+          <t xml:space="preserve">311726475</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Ebbesens Vej 10</t>
+          <t xml:space="preserve">Nyelandsvej 23</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1911</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027175</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>5031</v>
+        <v>2221</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726475</t>
+          <t xml:space="preserve">311726873</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-03</t>
+          <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,17 +8741,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 23</t>
+          <t xml:space="preserve">Grundtvigsvej 9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1864</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100026309</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>2221</v>
+        <v>10865</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726873</t>
+          <t xml:space="preserve">311727265</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-05</t>
+          <t xml:space="preserve">2033-12-06</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigsvej 9</t>
+          <t xml:space="preserve">La Cours Vej 2</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026309</t>
+          <t xml:space="preserve">100030249</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8835,11 +8835,11 @@
         </is>
       </c>
       <c r="J118">
-        <v>10865</v>
+        <v>5199</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727265</t>
+          <t xml:space="preserve">311727254</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">La Cours Vej 2</t>
+          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030249</t>
+          <t xml:space="preserve">100029769</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>5199</v>
+        <v>1176</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311727254</t>
+          <t xml:space="preserve">311733387</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-06</t>
+          <t xml:space="preserve">2034-01-16</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lauritz Sørensens Vej 1</t>
+          <t xml:space="preserve">Pile Alle 33</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029769</t>
+          <t xml:space="preserve">191032, 191033</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>1176</v>
+        <v>1248</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733387</t>
+          <t xml:space="preserve">311733392</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pile Alle 33</t>
+          <t xml:space="preserve">Finsensvej 92</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">191032, 191033</t>
+          <t xml:space="preserve">100029806</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>1248</v>
+        <v>3370</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733392</t>
+          <t xml:space="preserve">311734724</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-16</t>
+          <t xml:space="preserve">2034-01-20</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finsensvej 92</t>
+          <t xml:space="preserve">Falkoner Alle 130</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029806</t>
+          <t xml:space="preserve">100028184</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>3370</v>
+        <v>562</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311734724</t>
+          <t xml:space="preserve">311735174</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-20</t>
+          <t xml:space="preserve">2034-01-25</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkoner Alle 130</t>
+          <t xml:space="preserve">Falkonergårdsvej 21</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1959</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028184</t>
+          <t xml:space="preserve">100028183</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>562</v>
+        <v>375</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735174</t>
+          <t xml:space="preserve">311735114</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,30 +9266,30 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkonergårdsvej 21</t>
+          <t xml:space="preserve">Sofus Francks Vænge 28</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1959</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028183</t>
+          <t xml:space="preserve">100029540</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J124">
-        <v>375</v>
+        <v>856</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735114</t>
+          <t xml:space="preserve">311742694</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-25</t>
+          <t xml:space="preserve">2034-02-01</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 28</t>
+          <t xml:space="preserve">Sofus Francks Vænge 30</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9356,15 +9356,15 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>856</v>
+        <v>6815</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742694</t>
+          <t xml:space="preserve">311742695</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 30</t>
+          <t xml:space="preserve">Sofus Francks Vænge 34</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9431,15 +9431,15 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>6815</v>
+        <v>706</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742695</t>
+          <t xml:space="preserve">311742696</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofus Francks Vænge 34</t>
+          <t xml:space="preserve">Christian Paulsens Vej 26</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029540</t>
+          <t xml:space="preserve">100029283</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>706</v>
+        <v>2340</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742696</t>
+          <t xml:space="preserve">311736719</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-01</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 26</t>
+          <t xml:space="preserve">Godthåbsvej 21A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029283</t>
+          <t xml:space="preserve">100026096</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>2340</v>
+        <v>812</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736719</t>
+          <t xml:space="preserve">311736735</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 21A</t>
+          <t xml:space="preserve">Godthåbsvej 23</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9656,15 +9656,15 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J129">
-        <v>812</v>
+        <v>1290</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736735</t>
+          <t xml:space="preserve">311736733</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 23</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026096</t>
+          <t xml:space="preserve">100029324</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>1290</v>
+        <v>2412</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736733</t>
+          <t xml:space="preserve">311736741</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 37A</t>
+          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029324</t>
+          <t xml:space="preserve">100029349</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>2412</v>
+        <v>2532</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736741</t>
+          <t xml:space="preserve">311737441</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-06</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustav Johannsens Vej 50</t>
+          <t xml:space="preserve">Nyelandsvej 25B</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029349</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J132">
-        <v>2532</v>
+        <v>467</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737441</t>
+          <t xml:space="preserve">311738410</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-06</t>
+          <t xml:space="preserve">2034-02-12</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25B</t>
+          <t xml:space="preserve">Roskildevej 54A</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029110</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J133">
-        <v>467</v>
+        <v>382</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738410</t>
+          <t xml:space="preserve">311738404</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10031,15 +10031,15 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J134">
-        <v>382</v>
+        <v>759</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738404</t>
+          <t xml:space="preserve">311738403</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 54A</t>
+          <t xml:space="preserve">Lyøvej 12</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029110</t>
+          <t xml:space="preserve">100025884</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>759</v>
+        <v>654</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738403</t>
+          <t xml:space="preserve">311738624</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-12</t>
+          <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyøvej 12</t>
+          <t xml:space="preserve">Nyelandsvej 25A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,20 +10176,20 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025884</t>
+          <t xml:space="preserve">100025833</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J136">
-        <v>654</v>
+        <v>1086</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738624</t>
+          <t xml:space="preserve">311738883</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-13</t>
+          <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 25A</t>
+          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,20 +10251,20 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025833</t>
+          <t xml:space="preserve">100029465</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J137">
-        <v>1086</v>
+        <v>458</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738883</t>
+          <t xml:space="preserve">311740954</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-14</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10331,15 +10331,15 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J138">
-        <v>458</v>
+        <v>4137</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740954</t>
+          <t xml:space="preserve">311739450</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Chr. Hansens Vej 1</t>
+          <t xml:space="preserve">Nyelandsvej 51</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,20 +10401,20 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029465</t>
+          <t xml:space="preserve">100025875</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J139">
-        <v>4137</v>
+        <v>541</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739450</t>
+          <t xml:space="preserve">311739362</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 51</t>
+          <t xml:space="preserve">Nyelandsvej 75</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">100025875</t>
+          <t xml:space="preserve">100029459</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="J140">
-        <v>541</v>
+        <v>1009</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739362</t>
+          <t xml:space="preserve">311739367</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 75</t>
+          <t xml:space="preserve">Sankt Knuds Vej 32</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1903</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029459</t>
+          <t xml:space="preserve">100027037</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J141">
-        <v>1009</v>
+        <v>846</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739367</t>
+          <t xml:space="preserve">311739928</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Knuds Vej 32</t>
+          <t xml:space="preserve">Holger Danskes Vej 104</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027037</t>
+          <t xml:space="preserve">100028752</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J142">
-        <v>846</v>
+        <v>594</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739928</t>
+          <t xml:space="preserve">311740966</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-20</t>
+          <t xml:space="preserve">2034-02-26</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holger Danskes Vej 104</t>
+          <t xml:space="preserve">Rosenørns Alle 59</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1970</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100028752</t>
+          <t xml:space="preserve">100026419</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J143">
-        <v>594</v>
+        <v>1965</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740966</t>
+          <t xml:space="preserve">311741888</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-26</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,30 +10766,30 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenørns Alle 59</t>
+          <t xml:space="preserve">Svanholmsvej 15</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970</t>
+          <t xml:space="preserve">1905</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026419</t>
+          <t xml:space="preserve">100027101</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>1965</v>
+        <v>1287</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741888</t>
+          <t xml:space="preserve">311741757</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanholmsvej 15</t>
+          <t xml:space="preserve">Vagtelvej 58</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027101</t>
+          <t xml:space="preserve">100027314</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>1287</v>
+        <v>1134</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741757</t>
+          <t xml:space="preserve">311741762</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vagtelvej 58</t>
+          <t xml:space="preserve">Eversvej 2</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">100027314</t>
+          <t xml:space="preserve">100029822</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>1134</v>
+        <v>9353</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741762</t>
+          <t xml:space="preserve">311743570</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eversvej 2</t>
+          <t xml:space="preserve">Tesdorpfsvej 23</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029822</t>
+          <t xml:space="preserve">100029708</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>9353</v>
+        <v>291</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743570</t>
+          <t xml:space="preserve">311742345</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 23</t>
+          <t xml:space="preserve">Tesdorpfsvej 25</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029708</t>
+          <t xml:space="preserve">100029707</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>291</v>
+        <v>1491</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742345</t>
+          <t xml:space="preserve">311742340</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesdorpfsvej 25</t>
+          <t xml:space="preserve">Nimbusparken 26</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029707</t>
+          <t xml:space="preserve">100029646</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>1491</v>
+        <v>5305</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742340</t>
+          <t xml:space="preserve">311743895</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-03-08</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nimbusparken 26</t>
+          <t xml:space="preserve">Virginiavej 11</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029646</t>
+          <t xml:space="preserve">100026985</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -11235,11 +11235,11 @@
         </is>
       </c>
       <c r="J150">
-        <v>5305</v>
+        <v>814</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743895</t>
+          <t xml:space="preserve">311743940</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virginiavej 11</t>
+          <t xml:space="preserve">Flintholm Alle 25</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026985</t>
+          <t xml:space="preserve">100029803</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>814</v>
+        <v>3250</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743940</t>
+          <t xml:space="preserve">311744589</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-08</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 25</t>
+          <t xml:space="preserve">Flintholm Alle 35</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029803</t>
+          <t xml:space="preserve">100029802</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>3250</v>
+        <v>3280</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744589</t>
+          <t xml:space="preserve">311744599</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 35</t>
+          <t xml:space="preserve">Flintholm Alle 45</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029802</t>
+          <t xml:space="preserve">100029790</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11460,11 +11460,11 @@
         </is>
       </c>
       <c r="J153">
-        <v>3280</v>
+        <v>2615</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744599</t>
+          <t xml:space="preserve">311744608</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintholm Alle 45</t>
+          <t xml:space="preserve">Christian Paulsens Vej 32</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029790</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J154">
-        <v>2615</v>
+        <v>2505</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744608</t>
+          <t xml:space="preserve">311745373</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-03-14</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian Paulsens Vej 32</t>
+          <t xml:space="preserve">Elga Olgas Vej 5</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">100029824</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>2505</v>
+        <v>4407</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745373</t>
+          <t xml:space="preserve">311745450</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11661,22 +11661,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">147</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elga Olgas Vej 5</t>
+          <t xml:space="preserve">Lynge Bygade 60</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">3540</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029824</t>
+          <t xml:space="preserve">2252337</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>4407</v>
+        <v>534</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745450</t>
+          <t xml:space="preserve">311745449</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11736,22 +11736,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">147</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynge Bygade 60</t>
+          <t xml:space="preserve">Sønderjyllands Alle 10</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2252337</t>
+          <t xml:space="preserve">100029307</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -11760,11 +11760,11 @@
         </is>
       </c>
       <c r="J157">
-        <v>534</v>
+        <v>3120</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311745449</t>
+          <t xml:space="preserve">311767998</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderjyllands Alle 10</t>
+          <t xml:space="preserve">Nyelandsvej 85</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029307</t>
+          <t xml:space="preserve">100029472</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,21 +11835,21 @@
         </is>
       </c>
       <c r="J158">
-        <v>3120</v>
+        <v>4687</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767998</t>
+          <t xml:space="preserve">311746471</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Norca ApS</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-14</t>
+          <t xml:space="preserve">2034-03-19</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyelandsvej 85</t>
+          <t xml:space="preserve">Godthåbsvej 83</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029472</t>
+          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,21 +11910,21 @@
         </is>
       </c>
       <c r="J159">
-        <v>4687</v>
+        <v>13136</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746471</t>
+          <t xml:space="preserve">311746996</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norca ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-19</t>
+          <t xml:space="preserve">2034-03-21</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godthåbsvej 83</t>
+          <t xml:space="preserve">Frederiksvej 51</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">174465, 174466, 174468, 174469</t>
+          <t xml:space="preserve">100029085</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>13136</v>
+        <v>2080</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746996</t>
+          <t xml:space="preserve">311758493</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-21</t>
+          <t xml:space="preserve">2034-05-10</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksvej 51</t>
+          <t xml:space="preserve">Nordre Fasanvej 81</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029085</t>
+          <t xml:space="preserve">100029721</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>2080</v>
+        <v>787</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758493</t>
+          <t xml:space="preserve">311758487</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 81</t>
+          <t xml:space="preserve">Beringsvej 8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029721</t>
+          <t xml:space="preserve">100030255</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,21 +12135,21 @@
         </is>
       </c>
       <c r="J162">
-        <v>787</v>
+        <v>413</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758487</t>
+          <t xml:space="preserve">311926722</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-10</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beringsvej 8</t>
+          <t xml:space="preserve">Hoffmeyersvej 40</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030255</t>
+          <t xml:space="preserve">100029487</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>413</v>
+        <v>1071</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926722</t>
+          <t xml:space="preserve">311928517</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-18</t>
+          <t xml:space="preserve">2036-09-28</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hoffmeyersvej 40</t>
+          <t xml:space="preserve">Nordre Fasanvej 75</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029487</t>
+          <t xml:space="preserve">100029720</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>1071</v>
+        <v>1334</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928517</t>
+          <t xml:space="preserve">311928590</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Fasanvej 75</t>
+          <t xml:space="preserve">Svanemosegårdsvej 10</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000</t>
+          <t xml:space="preserve">1967</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100029720</t>
+          <t xml:space="preserve">100026430</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>1334</v>
+        <v>446</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311928590</t>
+          <t xml:space="preserve">311929077</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-28</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,17 +12416,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanemosegårdsvej 10</t>
+          <t xml:space="preserve">Segelckesvej 7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1967</t>
+          <t xml:space="preserve">2000</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100026430</t>
+          <t xml:space="preserve">100030239</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929077</t>
+          <t xml:space="preserve">311930766</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-30</t>
+          <t xml:space="preserve">2036-10-08</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
